--- a/data/trans_orig/P44-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P44-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2012</t>
+          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2012 (tasa de respuesta: 97,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>8772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23692</t>
+          <t>23116</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9841</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25406</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>22163</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44169</t>
+          <t>44539</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>243385</t>
+          <t>243961</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>258720</t>
+          <t>258305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274290</t>
+          <t>274090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>290349</t>
+          <t>289855</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>522604</t>
+          <t>522234</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>545446</t>
+          <t>544610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41339</t>
+          <t>41309</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26212</t>
+          <t>26395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48856</t>
+          <t>50877</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51454</t>
+          <t>52167</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84062</t>
+          <t>84125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>290302</t>
+          <t>290332</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>313677</t>
+          <t>313284</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346888</t>
+          <t>344867</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369532</t>
+          <t>369349</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>643323</t>
+          <t>643260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>675931</t>
+          <t>675218</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42641</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18195</t>
+          <t>16822</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39121</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43053</t>
+          <t>41415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74635</t>
+          <t>73438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>202459</t>
+          <t>202581</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>226168</t>
+          <t>226737</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>263913</t>
+          <t>263599</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>284839</t>
+          <t>286212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>473499</t>
+          <t>474696</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>505081</t>
+          <t>506719</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28486</t>
+          <t>29620</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55894</t>
+          <t>55655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40966</t>
+          <t>42268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54855</t>
+          <t>54876</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89409</t>
+          <t>90626</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>294336</t>
+          <t>294575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>321744</t>
+          <t>320610</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>428040</t>
+          <t>426738</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>450056</t>
+          <t>449991</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>729827</t>
+          <t>728610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>764381</t>
+          <t>764360</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92764</t>
+          <t>91941</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>138282</t>
+          <t>138120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89516</t>
+          <t>91432</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131398</t>
+          <t>133802</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>194216</t>
+          <t>196684</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>254540</t>
+          <t>256243</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1055767</t>
+          <t>1055929</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1101285</t>
+          <t>1102108</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1336082</t>
+          <t>1333678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1377964</t>
+          <t>1376048</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2406988</t>
+          <t>2405285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2467312</t>
+          <t>2464844</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2016</t>
+          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>22186</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44902</t>
+          <t>44726</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18825</t>
+          <t>17960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40210</t>
+          <t>38623</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,47 +2729,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>11,96%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>59418</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>44994</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>76499</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>9,67%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>12,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>59418</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>46505</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>76191</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>246638</t>
+          <t>246814</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269468</t>
+          <t>269354</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282687</t>
+          <t>284274</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>304937</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,47 +2842,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>88,04%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>94,44%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>555020</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>537939</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>569444</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>90,33%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>87,55%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>94,17%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>555020</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>538247</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>567933</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>87,6%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30141</t>
+          <t>28950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53475</t>
+          <t>53864</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23950</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49439</t>
+          <t>48695</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58643</t>
+          <t>58246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94338</t>
+          <t>93293</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>352366</t>
+          <t>351977</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375700</t>
+          <t>376891</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>418887</t>
+          <t>419631</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>444376</t>
+          <t>444410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>779829</t>
+          <t>780874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>815524</t>
+          <t>815921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>23436</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48117</t>
+          <t>44697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30785</t>
+          <t>30062</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39636</t>
+          <t>38698</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69439</t>
+          <t>67609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>235786</t>
+          <t>239206</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>260474</t>
+          <t>260467</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>266116</t>
+          <t>266839</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>284686</t>
+          <t>284913</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>511365</t>
+          <t>513195</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>541168</t>
+          <t>542106</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47839</t>
+          <t>45989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76709</t>
+          <t>74280</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25712</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52606</t>
+          <t>48810</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79309</t>
+          <t>78610</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116727</t>
+          <t>119036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341532</t>
+          <t>343961</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370402</t>
+          <t>372252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>455076</t>
+          <t>458872</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>481821</t>
+          <t>481970</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>809196</t>
+          <t>806887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>846614</t>
+          <t>847313</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141704</t>
+          <t>141503</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>191956</t>
+          <t>191432</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98308</t>
+          <t>99931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>141896</t>
+          <t>145022</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>250835</t>
+          <t>254479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>316911</t>
+          <t>319383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1207570</t>
+          <t>1208094</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1257822</t>
+          <t>1258023</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1453910</t>
+          <t>1450784</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1497498</t>
+          <t>1495875</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2678421</t>
+          <t>2675949</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2744497</t>
+          <t>2740853</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2023</t>
+          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2023 (tasa de respuesta: 98,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78048</t>
+          <t>79583</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106541</t>
+          <t>107086</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86316</t>
+          <t>86276</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>108959</t>
+          <t>110016</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174996</t>
+          <t>174145</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>208850</t>
+          <t>209958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>193478</t>
+          <t>192933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>221971</t>
+          <t>220436</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>241930</t>
+          <t>240873</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264573</t>
+          <t>264613</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>442058</t>
+          <t>440950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>475912</t>
+          <t>476763</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,25%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>221847</t>
+          <t>221810</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>544400</t>
+          <t>543660</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>113807</t>
+          <t>112929</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>141200</t>
+          <t>140062</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>340227</t>
+          <t>339959</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>772076</t>
+          <t>782929</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98926</t>
+          <t>99666</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421479</t>
+          <t>421516</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>287336</t>
+          <t>288474</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>314729</t>
+          <t>315607</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>299786</t>
+          <t>288933</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731635</t>
+          <t>731903</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,28%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93796</t>
+          <t>92479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123839</t>
+          <t>124907</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24256</t>
+          <t>22127</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126924</t>
+          <t>127181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73150</t>
+          <t>86401</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>245847</t>
+          <t>249623</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>198417</t>
+          <t>197349</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>228460</t>
+          <t>229777</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>373299</t>
+          <t>373042</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>475967</t>
+          <t>478096</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>576631</t>
+          <t>572855</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>749328</t>
+          <t>736077</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>89,5%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>174855</t>
+          <t>173710</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>210423</t>
+          <t>211230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>167528</t>
+          <t>165467</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>199961</t>
+          <t>201013</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>351539</t>
+          <t>350395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>400100</t>
+          <t>399884</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>234000</t>
+          <t>233193</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>269568</t>
+          <t>270713</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>328353</t>
+          <t>327301</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>360786</t>
+          <t>362847</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>572637</t>
+          <t>572853</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>621198</t>
+          <t>622342</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,98%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>613221</t>
+          <t>611744</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1137669</t>
+          <t>1112299</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>315898</t>
+          <t>303346</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>550702</t>
+          <t>548100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1034627</t>
+          <t>1025251</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1733043</t>
+          <t>1748115</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,69%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>572355</t>
+          <t>597725</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1096803</t>
+          <t>1098280</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1257260</t>
+          <t>1259862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1492064</t>
+          <t>1504616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1784943</t>
+          <t>1769871</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2483359</t>
+          <t>2492735</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P44-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P44-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8772</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>23810</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9149</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25606</t>
+          <t>25666</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22163</t>
+          <t>21891</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44539</t>
+          <t>43922</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>243961</t>
+          <t>243267</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>258305</t>
+          <t>257910</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274090</t>
+          <t>274030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289855</t>
+          <t>290547</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>522234</t>
+          <t>522851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>544610</t>
+          <t>544882</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18357</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41309</t>
+          <t>40952</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>27248</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50877</t>
+          <t>50562</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52167</t>
+          <t>49949</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84125</t>
+          <t>83481</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>290332</t>
+          <t>290689</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>313284</t>
+          <t>313119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>344867</t>
+          <t>345182</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369349</t>
+          <t>368496</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>643260</t>
+          <t>643904</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>675218</t>
+          <t>677436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18363</t>
+          <t>18420</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>42791</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39435</t>
+          <t>40415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41415</t>
+          <t>41905</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73438</t>
+          <t>75503</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>202581</t>
+          <t>202309</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>226737</t>
+          <t>226680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>263599</t>
+          <t>262619</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>286212</t>
+          <t>284102</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>474696</t>
+          <t>472631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>506719</t>
+          <t>506229</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29620</t>
+          <t>28800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55655</t>
+          <t>56165</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>19450</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42268</t>
+          <t>40777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54876</t>
+          <t>56005</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90626</t>
+          <t>90233</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>294575</t>
+          <t>294065</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320610</t>
+          <t>321430</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>426738</t>
+          <t>428229</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>449991</t>
+          <t>449556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>728610</t>
+          <t>729003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>764360</t>
+          <t>763231</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91941</t>
+          <t>92930</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>138120</t>
+          <t>136953</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91432</t>
+          <t>90234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133802</t>
+          <t>131805</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>196684</t>
+          <t>194689</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>256243</t>
+          <t>257344</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1055929</t>
+          <t>1057096</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1102108</t>
+          <t>1101119</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1333678</t>
+          <t>1335675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1376048</t>
+          <t>1377246</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2405285</t>
+          <t>2404184</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2464844</t>
+          <t>2466839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22186</t>
+          <t>22325</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44726</t>
+          <t>43958</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>17787</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38623</t>
+          <t>40256</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44994</t>
+          <t>45153</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76499</t>
+          <t>76495</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>246814</t>
+          <t>247582</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269354</t>
+          <t>269215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284274</t>
+          <t>282641</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304937</t>
+          <t>305110</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>537939</t>
+          <t>537943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>569444</t>
+          <t>569285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28950</t>
+          <t>29726</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53864</t>
+          <t>55248</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23916</t>
+          <t>24220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48695</t>
+          <t>49619</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58246</t>
+          <t>60363</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93293</t>
+          <t>95520</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351977</t>
+          <t>350593</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376891</t>
+          <t>376115</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>419631</t>
+          <t>418707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>444410</t>
+          <t>444106</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>780874</t>
+          <t>778647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>815921</t>
+          <t>813804</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23436</t>
+          <t>22926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44697</t>
+          <t>44846</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11988</t>
+          <t>12415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30062</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38698</t>
+          <t>40613</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67609</t>
+          <t>69327</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239206</t>
+          <t>239057</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>260467</t>
+          <t>260977</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>266839</t>
+          <t>266130</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>284913</t>
+          <t>284486</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>513195</t>
+          <t>511477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>542106</t>
+          <t>540191</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45989</t>
+          <t>47249</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74280</t>
+          <t>76476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25712</t>
+          <t>26626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48810</t>
+          <t>52405</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78610</t>
+          <t>79307</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119036</t>
+          <t>117918</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343961</t>
+          <t>341765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372252</t>
+          <t>370992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>458872</t>
+          <t>455277</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>481970</t>
+          <t>481056</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>806887</t>
+          <t>808005</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>847313</t>
+          <t>846616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,43%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141503</t>
+          <t>140424</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>191432</t>
+          <t>189496</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99931</t>
+          <t>98230</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145022</t>
+          <t>143470</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>254479</t>
+          <t>253370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>319383</t>
+          <t>322040</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1208094</t>
+          <t>1210030</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1258023</t>
+          <t>1259102</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1450784</t>
+          <t>1452336</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1495875</t>
+          <t>1497576</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2675949</t>
+          <t>2673292</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2740853</t>
+          <t>2741962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>92986</t>
+          <t>102195</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79583</t>
+          <t>87701</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107086</t>
+          <t>117677</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,32 +4656,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>97661</t>
+          <t>106458</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86276</t>
+          <t>94728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110016</t>
+          <t>119115</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>190647</t>
+          <t>208654</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174145</t>
+          <t>189357</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209958</t>
+          <t>228068</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>207033</t>
+          <t>227797</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>192933</t>
+          <t>212315</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220436</t>
+          <t>242291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>253228</t>
+          <t>270964</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>240873</t>
+          <t>258307</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264613</t>
+          <t>282694</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>460261</t>
+          <t>498760</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>440950</t>
+          <t>479346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>476763</t>
+          <t>518057</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>300019</t>
+          <t>329992</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>300019</t>
+          <t>329992</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>300019</t>
+          <t>329992</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>350889</t>
+          <t>377422</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>350889</t>
+          <t>377422</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>350889</t>
+          <t>377422</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>650908</t>
+          <t>707414</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>650908</t>
+          <t>707414</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>650908</t>
+          <t>707414</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,32 +4964,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>386980</t>
+          <t>153970</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>221810</t>
+          <t>135971</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>543660</t>
+          <t>173593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,32 +4999,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>127184</t>
+          <t>140333</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112929</t>
+          <t>125563</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140062</t>
+          <t>155389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>514163</t>
+          <t>294303</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>339959</t>
+          <t>271883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>782929</t>
+          <t>319010</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>256346</t>
+          <t>277126</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99666</t>
+          <t>257503</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421516</t>
+          <t>295125</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>301352</t>
+          <t>332036</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>288474</t>
+          <t>316980</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>315607</t>
+          <t>346806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>557699</t>
+          <t>609162</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>288933</t>
+          <t>584455</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731903</t>
+          <t>631582</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>69,91%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>643326</t>
+          <t>431096</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>643326</t>
+          <t>431096</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>643326</t>
+          <t>431096</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>428536</t>
+          <t>472369</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>428536</t>
+          <t>472369</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>428536</t>
+          <t>472369</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1071862</t>
+          <t>903465</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1071862</t>
+          <t>903465</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1071862</t>
+          <t>903465</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,32 +5307,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>107725</t>
+          <t>119104</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92479</t>
+          <t>103775</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124907</t>
+          <t>138259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5342,32 +5342,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>72306</t>
+          <t>85086</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22127</t>
+          <t>73277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127181</t>
+          <t>98535</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>180030</t>
+          <t>204190</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86401</t>
+          <t>183006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>249623</t>
+          <t>227865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>214531</t>
+          <t>246443</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>197349</t>
+          <t>227288</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>229777</t>
+          <t>261772</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>427917</t>
+          <t>252334</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>373042</t>
+          <t>238885</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>478096</t>
+          <t>264143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>642448</t>
+          <t>498777</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>572855</t>
+          <t>475102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>736077</t>
+          <t>519961</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>73,97%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>322256</t>
+          <t>365547</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>322256</t>
+          <t>365547</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>322256</t>
+          <t>365547</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>500223</t>
+          <t>337420</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>500223</t>
+          <t>337420</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>500223</t>
+          <t>337420</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>822478</t>
+          <t>702967</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>822478</t>
+          <t>702967</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>822478</t>
+          <t>702967</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>192807</t>
+          <t>200195</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>173710</t>
+          <t>182278</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>211230</t>
+          <t>219822</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>182272</t>
+          <t>198125</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>165467</t>
+          <t>179198</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>201013</t>
+          <t>216492</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>375079</t>
+          <t>398320</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>350395</t>
+          <t>373614</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>399884</t>
+          <t>427031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>251616</t>
+          <t>267144</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>233193</t>
+          <t>247517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>270713</t>
+          <t>285061</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>346042</t>
+          <t>366153</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>327301</t>
+          <t>347786</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362847</t>
+          <t>385080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>597658</t>
+          <t>633298</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>572853</t>
+          <t>604587</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>622342</t>
+          <t>658004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,78%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>444423</t>
+          <t>467339</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>444423</t>
+          <t>467339</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>444423</t>
+          <t>467339</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>528314</t>
+          <t>564278</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>528314</t>
+          <t>564278</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>528314</t>
+          <t>564278</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>972737</t>
+          <t>1031618</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>972737</t>
+          <t>1031618</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>972737</t>
+          <t>1031618</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>780497</t>
+          <t>575464</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>611744</t>
+          <t>540928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1112299</t>
+          <t>611536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>303346</t>
+          <t>501033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>548100</t>
+          <t>558655</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1259920</t>
+          <t>1105467</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1025251</t>
+          <t>1057958</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1748115</t>
+          <t>1152250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>929527</t>
+          <t>1018510</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>597725</t>
+          <t>982438</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1098280</t>
+          <t>1053046</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1328539</t>
+          <t>1221487</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1259862</t>
+          <t>1192834</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1504616</t>
+          <t>1250456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2258066</t>
+          <t>2239996</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1769871</t>
+          <t>2193213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2492735</t>
+          <t>2287505</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>68,38%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1710024</t>
+          <t>1593974</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1710024</t>
+          <t>1593974</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1710024</t>
+          <t>1593974</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1807962</t>
+          <t>1751489</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1807962</t>
+          <t>1751489</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1807962</t>
+          <t>1751489</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3517986</t>
+          <t>3345463</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3517986</t>
+          <t>3345463</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3517986</t>
+          <t>3345463</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
